--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S497"/>
+  <dimension ref="A1:S498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31725,6 +31725,69 @@
         <v>283.33</v>
       </c>
       <c r="S497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="C498" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="D498" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="E498" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="F498" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="G498" t="n">
+        <v>364.96</v>
+      </c>
+      <c r="H498" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="I498" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="J498" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="K498" t="n">
+        <v>361.72</v>
+      </c>
+      <c r="L498" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="M498" t="n">
+        <v>358.41</v>
+      </c>
+      <c r="N498" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="O498" t="n">
+        <v>315.45</v>
+      </c>
+      <c r="P498" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>287.92</v>
+      </c>
+      <c r="R498" t="n">
+        <v>298.55</v>
+      </c>
+      <c r="S498" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31741,7 +31804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36784,6 +36847,16 @@
       </c>
       <c r="B504" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -36952,28 +37025,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5860744402042501</v>
+        <v>-0.5834799334240309</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K2" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.13621443817797</v>
+        <v>0.1355168491423926</v>
       </c>
       <c r="M2" t="n">
-        <v>8.6791454147117</v>
+        <v>8.675477443168484</v>
       </c>
       <c r="N2" t="n">
-        <v>131.2027671218726</v>
+        <v>131.0451164265785</v>
       </c>
       <c r="O2" t="n">
-        <v>11.45437764009344</v>
+        <v>11.44749389283866</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6849323592592</v>
+        <v>388.6587360060918</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37030,28 +37103,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5036389321035544</v>
+        <v>-0.5005232261544631</v>
       </c>
       <c r="J3" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1054542627219449</v>
+        <v>0.1045316708244179</v>
       </c>
       <c r="M3" t="n">
-        <v>9.369242666452262</v>
+        <v>9.366495120995303</v>
       </c>
       <c r="N3" t="n">
-        <v>127.1211755531433</v>
+        <v>127.013725982064</v>
       </c>
       <c r="O3" t="n">
-        <v>11.27480268355696</v>
+        <v>11.27003664510742</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3720421770317</v>
+        <v>374.3401095932833</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37108,28 +37181,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2975951871676243</v>
+        <v>-0.2968557584013917</v>
       </c>
       <c r="J4" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K4" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04028967384383964</v>
+        <v>0.04024025638862971</v>
       </c>
       <c r="M4" t="n">
-        <v>8.547706901883133</v>
+        <v>8.53476802735165</v>
       </c>
       <c r="N4" t="n">
-        <v>127.090723725457</v>
+        <v>126.8437539029019</v>
       </c>
       <c r="O4" t="n">
-        <v>11.27345216539535</v>
+        <v>11.26249323653079</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5134337964457</v>
+        <v>369.5059845349385</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37186,28 +37259,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08599585274287407</v>
+        <v>-0.08544945132524465</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004063773271201887</v>
+        <v>0.004027404579221128</v>
       </c>
       <c r="M5" t="n">
-        <v>8.365982222529013</v>
+        <v>8.352281645706388</v>
       </c>
       <c r="N5" t="n">
-        <v>109.1874454248851</v>
+        <v>108.9725280689377</v>
       </c>
       <c r="O5" t="n">
-        <v>10.44927966057398</v>
+        <v>10.43899075911736</v>
       </c>
       <c r="P5" t="n">
-        <v>363.8891836170154</v>
+        <v>363.8836789798769</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37264,28 +37337,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08179739484920667</v>
+        <v>-0.0805775747554585</v>
       </c>
       <c r="J6" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006347782876459984</v>
+        <v>0.00618180551348857</v>
       </c>
       <c r="M6" t="n">
-        <v>6.595852119517327</v>
+        <v>6.589770856362727</v>
       </c>
       <c r="N6" t="n">
-        <v>63.09673935449685</v>
+        <v>62.99358564575699</v>
       </c>
       <c r="O6" t="n">
-        <v>7.943345602106008</v>
+        <v>7.936849856571371</v>
       </c>
       <c r="P6" t="n">
-        <v>363.0921863199596</v>
+        <v>363.0798974298257</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37342,28 +37415,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07633648274479919</v>
+        <v>-0.07436727614406473</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K7" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006726364884591107</v>
+        <v>0.006402248989976989</v>
       </c>
       <c r="M7" t="n">
-        <v>6.03499451570708</v>
+        <v>6.034347271706425</v>
       </c>
       <c r="N7" t="n">
-        <v>52.00474042487246</v>
+        <v>51.96202242817956</v>
       </c>
       <c r="O7" t="n">
-        <v>7.211431232763193</v>
+        <v>7.208468799140325</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4029812947027</v>
+        <v>361.3831648524018</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37420,28 +37493,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1724273602905522</v>
+        <v>-0.1701336359249372</v>
       </c>
       <c r="J8" t="n">
+        <v>497</v>
+      </c>
+      <c r="K8" t="n">
         <v>496</v>
       </c>
-      <c r="K8" t="n">
-        <v>495</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03805638113156284</v>
+        <v>0.03715583610058881</v>
       </c>
       <c r="M8" t="n">
-        <v>5.400391592690418</v>
+        <v>5.401240652092371</v>
       </c>
       <c r="N8" t="n">
-        <v>45.35093011815619</v>
+        <v>45.34386954807177</v>
       </c>
       <c r="O8" t="n">
-        <v>6.734309921451209</v>
+        <v>6.733785677319391</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0859486354952</v>
+        <v>363.0628562198609</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37498,28 +37571,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1041343821393228</v>
+        <v>-0.1030463054888535</v>
       </c>
       <c r="J9" t="n">
+        <v>497</v>
+      </c>
+      <c r="K9" t="n">
         <v>496</v>
       </c>
-      <c r="K9" t="n">
-        <v>495</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01859057366814953</v>
+        <v>0.01826866024216089</v>
       </c>
       <c r="M9" t="n">
-        <v>4.768777915871105</v>
+        <v>4.764812948841895</v>
       </c>
       <c r="N9" t="n">
-        <v>34.54597321289722</v>
+        <v>34.49531030453768</v>
       </c>
       <c r="O9" t="n">
-        <v>5.877582259134893</v>
+        <v>5.873270835278898</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3729466802451</v>
+        <v>361.3619923046317</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37576,28 +37649,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1153349541642763</v>
+        <v>-0.1148633267698482</v>
       </c>
       <c r="J10" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K10" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02569249497427717</v>
+        <v>0.02557874091675438</v>
       </c>
       <c r="M10" t="n">
-        <v>4.445799227281297</v>
+        <v>4.43963534465549</v>
       </c>
       <c r="N10" t="n">
-        <v>30.48329324705594</v>
+        <v>30.42528653141343</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5211677430645</v>
+        <v>5.515912121436801</v>
       </c>
       <c r="P10" t="n">
-        <v>362.6439094924892</v>
+        <v>362.6391630670261</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37654,28 +37727,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1666349207565196</v>
+        <v>-0.1658529463856494</v>
       </c>
       <c r="J11" t="n">
+        <v>497</v>
+      </c>
+      <c r="K11" t="n">
         <v>496</v>
       </c>
-      <c r="K11" t="n">
-        <v>495</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.04345368736528366</v>
+        <v>0.04320860938610449</v>
       </c>
       <c r="M11" t="n">
-        <v>4.935764899597405</v>
+        <v>4.930538784543576</v>
       </c>
       <c r="N11" t="n">
-        <v>36.87437491788302</v>
+        <v>36.80983619304796</v>
       </c>
       <c r="O11" t="n">
-        <v>6.072427432080437</v>
+        <v>6.067111025277843</v>
       </c>
       <c r="P11" t="n">
-        <v>363.9065733892132</v>
+        <v>363.8986983948403</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37732,28 +37805,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2157698319606302</v>
+        <v>-0.2158317569533287</v>
       </c>
       <c r="J12" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K12" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06415479699491178</v>
+        <v>0.06441574530758276</v>
       </c>
       <c r="M12" t="n">
-        <v>4.984462408884133</v>
+        <v>4.974816329434687</v>
       </c>
       <c r="N12" t="n">
-        <v>40.91400183428435</v>
+        <v>40.8317412391369</v>
       </c>
       <c r="O12" t="n">
-        <v>6.396405383829604</v>
+        <v>6.389971927883322</v>
       </c>
       <c r="P12" t="n">
-        <v>365.9535028444533</v>
+        <v>365.9541266982787</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37810,28 +37883,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2233662737452618</v>
+        <v>-0.2244687795116804</v>
       </c>
       <c r="J13" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K13" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05081406944309219</v>
+        <v>0.05145775128652463</v>
       </c>
       <c r="M13" t="n">
-        <v>5.839465963786128</v>
+        <v>5.83472030917024</v>
       </c>
       <c r="N13" t="n">
-        <v>56.14591244233266</v>
+        <v>56.05238630311796</v>
       </c>
       <c r="O13" t="n">
-        <v>7.493057616376152</v>
+        <v>7.486814162453745</v>
       </c>
       <c r="P13" t="n">
-        <v>367.4202104239467</v>
+        <v>367.4313174489129</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37888,28 +37961,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2303572656277785</v>
+        <v>-0.2321871620246435</v>
       </c>
       <c r="J14" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K14" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04649895090490519</v>
+        <v>0.04733836233188848</v>
       </c>
       <c r="M14" t="n">
-        <v>6.49852446890107</v>
+        <v>6.495360595471421</v>
       </c>
       <c r="N14" t="n">
-        <v>65.5537409016151</v>
+        <v>65.47540513689617</v>
       </c>
       <c r="O14" t="n">
-        <v>8.096526471371233</v>
+        <v>8.091687409736993</v>
       </c>
       <c r="P14" t="n">
-        <v>368.3542199263641</v>
+        <v>368.3726549364879</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37966,28 +38039,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.844358703135175</v>
+        <v>-1.848487894025268</v>
       </c>
       <c r="J15" t="n">
+        <v>497</v>
+      </c>
+      <c r="K15" t="n">
         <v>496</v>
       </c>
-      <c r="K15" t="n">
-        <v>495</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1271360596192747</v>
+        <v>0.1280309391903746</v>
       </c>
       <c r="M15" t="n">
-        <v>27.01954824004487</v>
+        <v>26.9978930435326</v>
       </c>
       <c r="N15" t="n">
-        <v>1408.350041314937</v>
+        <v>1405.783923194294</v>
       </c>
       <c r="O15" t="n">
-        <v>37.52799010491951</v>
+        <v>37.49378512759541</v>
       </c>
       <c r="P15" t="n">
-        <v>375.7687737955546</v>
+        <v>375.810371290075</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38044,28 +38117,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6154067706637769</v>
+        <v>-0.6285124390391077</v>
       </c>
       <c r="J16" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K16" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01123867015881053</v>
+        <v>0.01174452719395869</v>
       </c>
       <c r="M16" t="n">
-        <v>36.14662364083821</v>
+        <v>36.16558012677318</v>
       </c>
       <c r="N16" t="n">
-        <v>1994.200082908412</v>
+        <v>1992.885194837821</v>
       </c>
       <c r="O16" t="n">
-        <v>44.65646742531715</v>
+        <v>44.64174273970295</v>
       </c>
       <c r="P16" t="n">
-        <v>342.4744342162463</v>
+        <v>342.6074325352457</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38122,28 +38195,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.709750430005947</v>
+        <v>-1.720862541925484</v>
       </c>
       <c r="J17" t="n">
+        <v>497</v>
+      </c>
+      <c r="K17" t="n">
         <v>496</v>
       </c>
-      <c r="K17" t="n">
-        <v>495</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.2093136282102643</v>
+        <v>0.2116012549447458</v>
       </c>
       <c r="M17" t="n">
-        <v>18.38998415356411</v>
+        <v>18.43733827021594</v>
       </c>
       <c r="N17" t="n">
-        <v>661.0586323506067</v>
+        <v>661.6839788703129</v>
       </c>
       <c r="O17" t="n">
-        <v>25.71106050614417</v>
+        <v>25.72321867244286</v>
       </c>
       <c r="P17" t="n">
-        <v>364.2633461857795</v>
+        <v>364.3758562684874</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38200,28 +38273,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.434317794595492</v>
+        <v>-1.441641787669782</v>
       </c>
       <c r="J18" t="n">
+        <v>497</v>
+      </c>
+      <c r="K18" t="n">
         <v>496</v>
       </c>
-      <c r="K18" t="n">
-        <v>495</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1844822494876454</v>
+        <v>0.1863546111559982</v>
       </c>
       <c r="M18" t="n">
-        <v>16.9871660625676</v>
+        <v>17.00980658085999</v>
       </c>
       <c r="N18" t="n">
-        <v>544.4241672682964</v>
+        <v>544.177172950781</v>
       </c>
       <c r="O18" t="n">
-        <v>23.33289881837009</v>
+        <v>23.32760538398189</v>
       </c>
       <c r="P18" t="n">
-        <v>356.975178950792</v>
+        <v>357.0493343473996</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38259,7 +38332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S497"/>
+  <dimension ref="A1:S498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86379,6 +86452,103 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-41.031509790401415,172.110972621801</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-41.03082605467549,172.11099435288892</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-41.030147150290816,172.11095898489555</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-41.029473638213155,172.11085989977158</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-41.02880192230446,172.1107395367534</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-41.028129568443255,172.11062662116217</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-41.02745669684344,172.11051973428394</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-41.02678043146843,172.1104530392347</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-41.02610687948321,172.11035562899474</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-41.02543507862241,172.11023769711045</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-41.02476067532786,172.11014823202137</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-41.02408621376001,172.11005935734815</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-41.02341213611651,172.1099659921867</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-41.02266987252958,172.11034343785104</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>-41.021924672095295,172.11037155986114</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>-41.02127010173295,172.11011184220683</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>-41.02065350841063,172.10971632488497</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S498"/>
+  <dimension ref="A1:S501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31788,6 +31788,195 @@
         <v>298.55</v>
       </c>
       <c r="S498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="C499" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="D499" t="n">
+        <v>356.94</v>
+      </c>
+      <c r="E499" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="F499" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="G499" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="H499" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="I499" t="n">
+        <v>356.19</v>
+      </c>
+      <c r="J499" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="K499" t="n">
+        <v>359.84</v>
+      </c>
+      <c r="L499" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="M499" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="N499" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="O499" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="P499" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>320</v>
+      </c>
+      <c r="R499" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>375</v>
+      </c>
+      <c r="C500" t="n">
+        <v>366.91</v>
+      </c>
+      <c r="D500" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="E500" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="F500" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="G500" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="H500" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="I500" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="J500" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="K500" t="n">
+        <v>361.61</v>
+      </c>
+      <c r="L500" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="M500" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="N500" t="n">
+        <v>358.51</v>
+      </c>
+      <c r="O500" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="P500" t="n">
+        <v>349.53</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="R500" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="C501" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="D501" t="n">
+        <v>360.92</v>
+      </c>
+      <c r="E501" t="n">
+        <v>356.54</v>
+      </c>
+      <c r="F501" t="n">
+        <v>353.27</v>
+      </c>
+      <c r="G501" t="n">
+        <v>351.08</v>
+      </c>
+      <c r="H501" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="I501" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="J501" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="K501" t="n">
+        <v>361.26</v>
+      </c>
+      <c r="L501" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="M501" t="n">
+        <v>357.19</v>
+      </c>
+      <c r="N501" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="O501" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="P501" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>339.32</v>
+      </c>
+      <c r="R501" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="S501" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31804,7 +31993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B505"/>
+  <dimension ref="A1:B508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36857,6 +37046,36 @@
       </c>
       <c r="B505" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -37025,28 +37244,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5834799334240309</v>
+        <v>-0.5814324987683008</v>
       </c>
       <c r="J2" t="n">
+        <v>500</v>
+      </c>
+      <c r="K2" t="n">
         <v>497</v>
       </c>
-      <c r="K2" t="n">
-        <v>494</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1355168491423926</v>
+        <v>0.1359924479279374</v>
       </c>
       <c r="M2" t="n">
-        <v>8.675477443168484</v>
+        <v>8.63397172535357</v>
       </c>
       <c r="N2" t="n">
-        <v>131.0451164265785</v>
+        <v>130.2853838994178</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44749389283866</v>
+        <v>11.41426230202451</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6587360060918</v>
+        <v>388.6379556020606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37103,28 +37322,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5005232261544631</v>
+        <v>-0.4948514339792219</v>
       </c>
       <c r="J3" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1045316708244179</v>
+        <v>0.1033421000430765</v>
       </c>
       <c r="M3" t="n">
-        <v>9.366495120995303</v>
+        <v>9.338853572586492</v>
       </c>
       <c r="N3" t="n">
-        <v>127.013725982064</v>
+        <v>126.4188265073909</v>
       </c>
       <c r="O3" t="n">
-        <v>11.27003664510742</v>
+        <v>11.24361269821186</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3401095932833</v>
+        <v>374.2816603541276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37181,28 +37400,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2968557584013917</v>
+        <v>-0.2988127077433479</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04024025638862971</v>
+        <v>0.04118285979716685</v>
       </c>
       <c r="M4" t="n">
-        <v>8.53476802735165</v>
+        <v>8.494405579038178</v>
       </c>
       <c r="N4" t="n">
-        <v>126.8437539029019</v>
+        <v>126.1277797086609</v>
       </c>
       <c r="O4" t="n">
-        <v>11.26249323653079</v>
+        <v>11.23066247861901</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5059845349385</v>
+        <v>369.5257968827975</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37259,28 +37478,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08544945132524465</v>
+        <v>-0.0910616377433365</v>
       </c>
       <c r="J5" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K5" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004027404579221128</v>
+        <v>0.004616114127766968</v>
       </c>
       <c r="M5" t="n">
-        <v>8.352281645706388</v>
+        <v>8.333478641157926</v>
       </c>
       <c r="N5" t="n">
-        <v>108.9725280689377</v>
+        <v>108.4871546215217</v>
       </c>
       <c r="O5" t="n">
-        <v>10.43899075911736</v>
+        <v>10.41571671185049</v>
       </c>
       <c r="P5" t="n">
-        <v>363.8836789798769</v>
+        <v>363.9405409548068</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37337,28 +37556,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0805775747554585</v>
+        <v>-0.08741373334339347</v>
       </c>
       <c r="J6" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K6" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00618180551348857</v>
+        <v>0.007319836039963112</v>
       </c>
       <c r="M6" t="n">
-        <v>6.589770856362727</v>
+        <v>6.5870868354585</v>
       </c>
       <c r="N6" t="n">
-        <v>62.99358564575699</v>
+        <v>62.87249070172277</v>
       </c>
       <c r="O6" t="n">
-        <v>7.936849856571371</v>
+        <v>7.929217534014486</v>
       </c>
       <c r="P6" t="n">
-        <v>363.0798974298257</v>
+        <v>363.1491763924573</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37415,28 +37634,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07436727614406473</v>
+        <v>-0.08146951634623845</v>
       </c>
       <c r="J7" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K7" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006402248989976989</v>
+        <v>0.007717787429814438</v>
       </c>
       <c r="M7" t="n">
-        <v>6.034347271706425</v>
+        <v>6.036881889679047</v>
       </c>
       <c r="N7" t="n">
-        <v>51.96202242817956</v>
+        <v>51.93667991126738</v>
       </c>
       <c r="O7" t="n">
-        <v>7.208468799140325</v>
+        <v>7.206710755349307</v>
       </c>
       <c r="P7" t="n">
-        <v>361.3831648524018</v>
+        <v>361.4550679012517</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37493,28 +37712,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1701336359249372</v>
+        <v>-0.1728654498035631</v>
       </c>
       <c r="J8" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03715583610058881</v>
+        <v>0.03869586045874651</v>
       </c>
       <c r="M8" t="n">
-        <v>5.401240652092371</v>
+        <v>5.385678299926123</v>
       </c>
       <c r="N8" t="n">
-        <v>45.34386954807177</v>
+        <v>45.1158840774198</v>
       </c>
       <c r="O8" t="n">
-        <v>6.733785677319391</v>
+        <v>6.716835867982766</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0628562198609</v>
+        <v>363.0905272273993</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37571,28 +37790,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1030463054888535</v>
+        <v>-0.1055580631779008</v>
       </c>
       <c r="J9" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K9" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01826866024216089</v>
+        <v>0.01934809461677534</v>
       </c>
       <c r="M9" t="n">
-        <v>4.764812948841895</v>
+        <v>4.751531013931969</v>
       </c>
       <c r="N9" t="n">
-        <v>34.49531030453768</v>
+        <v>34.32229081196314</v>
       </c>
       <c r="O9" t="n">
-        <v>5.873270835278898</v>
+        <v>5.858522920665511</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3619923046317</v>
+        <v>361.3874277017175</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37649,28 +37868,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1148633267698482</v>
+        <v>-0.1147039694850957</v>
       </c>
       <c r="J10" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K10" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02557874091675438</v>
+        <v>0.02578940905372917</v>
       </c>
       <c r="M10" t="n">
-        <v>4.43963534465549</v>
+        <v>4.417471971935844</v>
       </c>
       <c r="N10" t="n">
-        <v>30.42528653141343</v>
+        <v>30.2461346221105</v>
       </c>
       <c r="O10" t="n">
-        <v>5.515912121436801</v>
+        <v>5.499648590783824</v>
       </c>
       <c r="P10" t="n">
-        <v>362.6391630670261</v>
+        <v>362.6375450764602</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37727,28 +37946,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1658529463856494</v>
+        <v>-0.1643825771258464</v>
       </c>
       <c r="J11" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K11" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04320860938610449</v>
+        <v>0.04292511826358902</v>
       </c>
       <c r="M11" t="n">
-        <v>4.930538784543576</v>
+        <v>4.909631968831516</v>
       </c>
       <c r="N11" t="n">
-        <v>36.80983619304796</v>
+        <v>36.60355447162046</v>
       </c>
       <c r="O11" t="n">
-        <v>6.067111025277843</v>
+        <v>6.050087145787279</v>
       </c>
       <c r="P11" t="n">
-        <v>363.8986983948403</v>
+        <v>363.8837991849206</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37805,28 +38024,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2158317569533287</v>
+        <v>-0.2197690238437931</v>
       </c>
       <c r="J12" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K12" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06441574530758276</v>
+        <v>0.06720421324295045</v>
       </c>
       <c r="M12" t="n">
-        <v>4.974816329434687</v>
+        <v>4.969000516564691</v>
       </c>
       <c r="N12" t="n">
-        <v>40.8317412391369</v>
+        <v>40.67395183277283</v>
       </c>
       <c r="O12" t="n">
-        <v>6.389971927883322</v>
+        <v>6.37761333358905</v>
       </c>
       <c r="P12" t="n">
-        <v>365.9541266982787</v>
+        <v>365.9940127497392</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37883,28 +38102,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2244687795116804</v>
+        <v>-0.2299471386722668</v>
       </c>
       <c r="J13" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K13" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05145775128652463</v>
+        <v>0.05429251588967909</v>
       </c>
       <c r="M13" t="n">
-        <v>5.83472030917024</v>
+        <v>5.834158382707034</v>
       </c>
       <c r="N13" t="n">
-        <v>56.05238630311796</v>
+        <v>55.88126329627688</v>
       </c>
       <c r="O13" t="n">
-        <v>7.486814162453745</v>
+        <v>7.475377134049952</v>
       </c>
       <c r="P13" t="n">
-        <v>367.4313174489129</v>
+        <v>367.4868176287611</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37961,28 +38180,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2321871620246435</v>
+        <v>-0.2364099869284923</v>
       </c>
       <c r="J14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04733836233188848</v>
+        <v>0.04944674734777954</v>
       </c>
       <c r="M14" t="n">
-        <v>6.495360595471421</v>
+        <v>6.479307662916868</v>
       </c>
       <c r="N14" t="n">
-        <v>65.47540513689617</v>
+        <v>65.18740587706149</v>
       </c>
       <c r="O14" t="n">
-        <v>8.091687409736993</v>
+        <v>8.073871802119569</v>
       </c>
       <c r="P14" t="n">
-        <v>368.3726549364879</v>
+        <v>368.4154298401712</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38039,28 +38258,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.848487894025268</v>
+        <v>-1.816437002653964</v>
       </c>
       <c r="J15" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K15" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1280309391903746</v>
+        <v>0.1249837291071368</v>
       </c>
       <c r="M15" t="n">
-        <v>26.9978930435326</v>
+        <v>26.94438838698438</v>
       </c>
       <c r="N15" t="n">
-        <v>1405.783923194294</v>
+        <v>1402.842866497171</v>
       </c>
       <c r="O15" t="n">
-        <v>37.49378512759541</v>
+        <v>37.45454400332717</v>
       </c>
       <c r="P15" t="n">
-        <v>375.810371290075</v>
+        <v>375.4855964762238</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38117,28 +38336,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6285124390391077</v>
+        <v>-0.6107518499571918</v>
       </c>
       <c r="J16" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K16" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01174452719395869</v>
+        <v>0.01120947371027814</v>
       </c>
       <c r="M16" t="n">
-        <v>36.16558012677318</v>
+        <v>36.022873840931</v>
       </c>
       <c r="N16" t="n">
-        <v>1992.885194837821</v>
+        <v>1983.191012785047</v>
       </c>
       <c r="O16" t="n">
-        <v>44.64174273970295</v>
+        <v>44.53303282716154</v>
       </c>
       <c r="P16" t="n">
-        <v>342.6074325352457</v>
+        <v>342.4260560645951</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38195,28 +38414,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.720862541925484</v>
+        <v>-1.706477341329539</v>
       </c>
       <c r="J17" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K17" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2116012549447458</v>
+        <v>0.2103083111773866</v>
       </c>
       <c r="M17" t="n">
-        <v>18.43733827021594</v>
+        <v>18.3794819034638</v>
       </c>
       <c r="N17" t="n">
-        <v>661.6839788703129</v>
+        <v>659.259202531744</v>
       </c>
       <c r="O17" t="n">
-        <v>25.72321867244286</v>
+        <v>25.67604335819178</v>
       </c>
       <c r="P17" t="n">
-        <v>364.3758562684874</v>
+        <v>364.2292899262619</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38273,28 +38492,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.441641787669782</v>
+        <v>-1.434315770614757</v>
       </c>
       <c r="J18" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K18" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1863546111559982</v>
+        <v>0.1863714840461287</v>
       </c>
       <c r="M18" t="n">
-        <v>17.00980658085999</v>
+        <v>16.94613919266722</v>
       </c>
       <c r="N18" t="n">
-        <v>544.177172950781</v>
+        <v>541.4897776302231</v>
       </c>
       <c r="O18" t="n">
-        <v>23.32760538398189</v>
+        <v>23.269932909878</v>
       </c>
       <c r="P18" t="n">
-        <v>357.0493343473996</v>
+        <v>356.974668689276</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38332,7 +38551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S498"/>
+  <dimension ref="A1:S501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86549,6 +86768,297 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-41.03150595391053,172.11101789798244</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-41.030823901018934,172.11101976875761</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-41.030140318664785,172.11103960556022</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-41.02946615551668,172.11094820332795</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-41.02879363830725,172.1108372961961</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-41.02811971184678,172.1107429383538</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-41.027448863712294,172.11061217242025</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-41.0267749026878,172.11051816940133</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-41.02610459177038,172.11038222005</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-41.025433145269325,172.1102599118928</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-41.02475569798435,172.110205422686</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-41.024082655594135,172.110100241169</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-41.02341151909742,172.10997308179492</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-41.02273786118594,172.1098986643475</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>-41.0220240835689,172.10993796872373</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>-41.021356557021875,172.1097477790168</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>-41.02069999663827,172.10952056322645</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-41.03150423098976,172.11103823088732</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-41.03082321986126,172.11102780726463</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-41.030144876427435,172.11098581904815</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-41.0294670971181,172.1109370915026</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-41.02879151470568,172.11086235665414</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-41.028116406254526,172.11078194716077</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-41.02744726101645,172.11063108559136</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-41.02677542446178,172.11051202281618</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-41.02610660495799,172.1103588199215</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-41.025434965500814,172.1102389969116</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-41.02475748736319,172.1101848624067</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-41.024084475813765,172.11007932661377</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>-41.023413575826034,172.10994944976693</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>-41.022747056897856,172.10983850618572</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>-41.02208147474119,172.10968764865885</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>-41.0214045273484,172.10954577347735</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>-41.020739181237225,172.10935555579852</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-41.03150295883083,172.11105324413626</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-41.03082093597556,172.11105475990453</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-41.03014430545635,172.11099255713907</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-41.02946699694778,172.1109382736117</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-41.02879079348126,172.11087086775277</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-41.02811566499869,172.1107906945897</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-41.02744673012277,172.1106373505791</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-41.02677455149359,172.1105223065259</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-41.026105801717044,172.11036815633656</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-41.02543460556833,172.1102431326424</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-41.02475775474132,172.11018179018095</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-41.024084959148276,172.1100737730311</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>-41.02341471730831,172.1099363339908</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>-41.02274835783904,172.10982999543674</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>-41.02208528514066,172.10967102893963</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>-41.021408623674326,172.1095285235528</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>-41.02074152583771,172.1093456825832</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S501"/>
+  <dimension ref="A1:S503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31977,6 +31977,132 @@
         <v>331.21</v>
       </c>
       <c r="S501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="C502" t="n">
+        <v>366.37</v>
+      </c>
+      <c r="D502" t="n">
+        <v>361.89</v>
+      </c>
+      <c r="E502" t="n">
+        <v>357.64</v>
+      </c>
+      <c r="F502" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="G502" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="H502" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="I502" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="J502" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="K502" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="L502" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="M502" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="N502" t="n">
+        <v>359.08</v>
+      </c>
+      <c r="O502" t="n">
+        <v>359.98</v>
+      </c>
+      <c r="P502" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="R502" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="C503" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="D503" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="E503" t="n">
+        <v>355.58</v>
+      </c>
+      <c r="F503" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="G503" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="H503" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="I503" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="J503" t="n">
+        <v>359.31</v>
+      </c>
+      <c r="K503" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="L503" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="M503" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="N503" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="O503" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="P503" t="n">
+        <v>354.76</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>342.61</v>
+      </c>
+      <c r="R503" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="S503" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31993,7 +32119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37076,6 +37202,26 @@
       </c>
       <c r="B508" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -37244,28 +37390,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5814324987683008</v>
+        <v>-0.5809824459715922</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1359924479279374</v>
+        <v>0.136691123102944</v>
       </c>
       <c r="M2" t="n">
-        <v>8.63397172535357</v>
+        <v>8.601722037796609</v>
       </c>
       <c r="N2" t="n">
-        <v>130.2853838994178</v>
+        <v>129.7652338273957</v>
       </c>
       <c r="O2" t="n">
-        <v>11.41426230202451</v>
+        <v>11.39145442107353</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6379556020606</v>
+        <v>388.6333661360567</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37322,28 +37468,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4948514339792219</v>
+        <v>-0.4923387462446366</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1033421000430765</v>
+        <v>0.1030544107993828</v>
       </c>
       <c r="M3" t="n">
-        <v>9.338853572586492</v>
+        <v>9.314019412760807</v>
       </c>
       <c r="N3" t="n">
-        <v>126.4188265073909</v>
+        <v>125.9702996078192</v>
       </c>
       <c r="O3" t="n">
-        <v>11.24361269821186</v>
+        <v>11.22364912173484</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2816603541276</v>
+        <v>374.2556858400893</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37400,28 +37546,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2988127077433479</v>
+        <v>-0.2993366962312684</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04118285979716685</v>
+        <v>0.04161819460409644</v>
       </c>
       <c r="M4" t="n">
-        <v>8.494405579038178</v>
+        <v>8.464602411443531</v>
       </c>
       <c r="N4" t="n">
-        <v>126.1277797086609</v>
+        <v>125.6317441906521</v>
       </c>
       <c r="O4" t="n">
-        <v>11.23066247861901</v>
+        <v>11.2085567398596</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5257968827975</v>
+        <v>369.5311338497583</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37478,28 +37624,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0910616377433365</v>
+        <v>-0.09449521703640701</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004616114127766968</v>
+        <v>0.005001758329604922</v>
       </c>
       <c r="M5" t="n">
-        <v>8.333478641157926</v>
+        <v>8.319411848754561</v>
       </c>
       <c r="N5" t="n">
-        <v>108.4871546215217</v>
+        <v>108.15420429864</v>
       </c>
       <c r="O5" t="n">
-        <v>10.41571671185049</v>
+        <v>10.39972135677875</v>
       </c>
       <c r="P5" t="n">
-        <v>363.9405409548068</v>
+        <v>363.9754629763003</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37556,28 +37702,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08741373334339347</v>
+        <v>-0.09309863461175125</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007319836039963112</v>
+        <v>0.008322415070043832</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5870868354585</v>
+        <v>6.591253357931664</v>
       </c>
       <c r="N6" t="n">
-        <v>62.87249070172277</v>
+        <v>62.88280296880134</v>
       </c>
       <c r="O6" t="n">
-        <v>7.929217534014486</v>
+        <v>7.929867777510627</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1491763924573</v>
+        <v>363.2069816348718</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37634,28 +37780,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08146951634623845</v>
+        <v>-0.08785460346308187</v>
       </c>
       <c r="J7" t="n">
+        <v>502</v>
+      </c>
+      <c r="K7" t="n">
         <v>500</v>
       </c>
-      <c r="K7" t="n">
-        <v>498</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.007717787429814438</v>
+        <v>0.008973726870686538</v>
       </c>
       <c r="M7" t="n">
-        <v>6.036881889679047</v>
+        <v>6.04734464444762</v>
       </c>
       <c r="N7" t="n">
-        <v>51.93667991126738</v>
+        <v>52.05957553027004</v>
       </c>
       <c r="O7" t="n">
-        <v>7.206710755349307</v>
+        <v>7.215232188243843</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4550679012517</v>
+        <v>361.5199250838148</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37712,28 +37858,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1728654498035631</v>
+        <v>-0.1757884443574569</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K8" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03869586045874651</v>
+        <v>0.04019218411286285</v>
       </c>
       <c r="M8" t="n">
-        <v>5.385678299926123</v>
+        <v>5.38210371381911</v>
       </c>
       <c r="N8" t="n">
-        <v>45.1158840774198</v>
+        <v>45.00539882583298</v>
       </c>
       <c r="O8" t="n">
-        <v>6.716835867982766</v>
+        <v>6.708606325149284</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0905272273993</v>
+        <v>363.1202329892569</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37790,28 +37936,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1055580631779008</v>
+        <v>-0.1080182153031656</v>
       </c>
       <c r="J9" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01934809461677534</v>
+        <v>0.02036253785285558</v>
       </c>
       <c r="M9" t="n">
-        <v>4.751531013931969</v>
+        <v>4.747461785092075</v>
       </c>
       <c r="N9" t="n">
-        <v>34.32229081196314</v>
+        <v>34.23487676328423</v>
       </c>
       <c r="O9" t="n">
-        <v>5.858522920665511</v>
+        <v>5.851057747389289</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3874277017175</v>
+        <v>361.4124305874868</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37868,28 +38014,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1147039694850957</v>
+        <v>-0.1148799534512547</v>
       </c>
       <c r="J10" t="n">
+        <v>502</v>
+      </c>
+      <c r="K10" t="n">
         <v>500</v>
       </c>
-      <c r="K10" t="n">
-        <v>498</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02578940905372917</v>
+        <v>0.02605606461379162</v>
       </c>
       <c r="M10" t="n">
-        <v>4.417471971935844</v>
+        <v>4.400759597724655</v>
       </c>
       <c r="N10" t="n">
-        <v>30.2461346221105</v>
+        <v>30.1254045427888</v>
       </c>
       <c r="O10" t="n">
-        <v>5.499648590783824</v>
+        <v>5.48866145273953</v>
       </c>
       <c r="P10" t="n">
-        <v>362.6375450764602</v>
+        <v>362.639333025522</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37946,28 +38092,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1643825771258464</v>
+        <v>-0.1623860908400693</v>
       </c>
       <c r="J11" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K11" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04292511826358902</v>
+        <v>0.04219912952694371</v>
       </c>
       <c r="M11" t="n">
-        <v>4.909631968831516</v>
+        <v>4.901837222542068</v>
       </c>
       <c r="N11" t="n">
-        <v>36.60355447162046</v>
+        <v>36.48973321604409</v>
       </c>
       <c r="O11" t="n">
-        <v>6.050087145787279</v>
+        <v>6.040673241952762</v>
       </c>
       <c r="P11" t="n">
-        <v>363.8837991849206</v>
+        <v>363.8635064631247</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38024,28 +38170,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2197690238437931</v>
+        <v>-0.2214005447031528</v>
       </c>
       <c r="J12" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06720421324295045</v>
+        <v>0.06858177410213173</v>
       </c>
       <c r="M12" t="n">
-        <v>4.969000516564691</v>
+        <v>4.959150883228225</v>
       </c>
       <c r="N12" t="n">
-        <v>40.67395183277283</v>
+        <v>40.53381958439284</v>
       </c>
       <c r="O12" t="n">
-        <v>6.37761333358905</v>
+        <v>6.366617593698623</v>
       </c>
       <c r="P12" t="n">
-        <v>365.9940127497392</v>
+        <v>366.0105994423651</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38102,28 +38248,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2299471386722668</v>
+        <v>-0.2323730271987724</v>
       </c>
       <c r="J13" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05429251588967909</v>
+        <v>0.05572928272963062</v>
       </c>
       <c r="M13" t="n">
-        <v>5.834158382707034</v>
+        <v>5.826152839459023</v>
       </c>
       <c r="N13" t="n">
-        <v>55.88126329627688</v>
+        <v>55.70685539653831</v>
       </c>
       <c r="O13" t="n">
-        <v>7.475377134049952</v>
+        <v>7.463702525994609</v>
       </c>
       <c r="P13" t="n">
-        <v>367.4868176287611</v>
+        <v>367.5114807117532</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38180,28 +38326,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2364099869284923</v>
+        <v>-0.2381618869668374</v>
       </c>
       <c r="J14" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K14" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04944674734777954</v>
+        <v>0.05048545804743487</v>
       </c>
       <c r="M14" t="n">
-        <v>6.479307662916868</v>
+        <v>6.46292403073757</v>
       </c>
       <c r="N14" t="n">
-        <v>65.18740587706149</v>
+        <v>64.95371393389649</v>
       </c>
       <c r="O14" t="n">
-        <v>8.073871802119569</v>
+        <v>8.05938669713127</v>
       </c>
       <c r="P14" t="n">
-        <v>368.4154298401712</v>
+        <v>368.4332385692349</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38258,28 +38404,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.816437002653964</v>
+        <v>-1.793115409946036</v>
       </c>
       <c r="J15" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K15" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1249837291071368</v>
+        <v>0.1226535259516264</v>
       </c>
       <c r="M15" t="n">
-        <v>26.94438838698438</v>
+        <v>26.91617274027333</v>
       </c>
       <c r="N15" t="n">
-        <v>1402.842866497171</v>
+        <v>1401.642159862788</v>
       </c>
       <c r="O15" t="n">
-        <v>37.45454400332717</v>
+        <v>37.43851172072399</v>
       </c>
       <c r="P15" t="n">
-        <v>375.4855964762238</v>
+        <v>375.2484544916842</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38336,28 +38482,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6107518499571918</v>
+        <v>-0.5911001960919841</v>
       </c>
       <c r="J16" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K16" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01120947371027814</v>
+        <v>0.0105692089622168</v>
       </c>
       <c r="M16" t="n">
-        <v>36.022873840931</v>
+        <v>35.96161618444813</v>
       </c>
       <c r="N16" t="n">
-        <v>1983.191012785047</v>
+        <v>1978.323917844041</v>
       </c>
       <c r="O16" t="n">
-        <v>44.53303282716154</v>
+        <v>44.478353362552</v>
       </c>
       <c r="P16" t="n">
-        <v>342.4260560645951</v>
+        <v>342.2247641689645</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38414,28 +38560,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.706477341329539</v>
+        <v>-1.69051835393095</v>
       </c>
       <c r="J17" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K17" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2103083111773866</v>
+        <v>0.2079331566083747</v>
       </c>
       <c r="M17" t="n">
-        <v>18.3794819034638</v>
+        <v>18.3650231289943</v>
       </c>
       <c r="N17" t="n">
-        <v>659.259202531744</v>
+        <v>658.6685930419802</v>
       </c>
       <c r="O17" t="n">
-        <v>25.67604335819178</v>
+        <v>25.66453960315634</v>
       </c>
       <c r="P17" t="n">
-        <v>364.2292899262619</v>
+        <v>364.0662002939503</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38492,28 +38638,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.434315770614757</v>
+        <v>-1.424694218137992</v>
       </c>
       <c r="J18" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K18" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1863714840461287</v>
+        <v>0.1852660745733129</v>
       </c>
       <c r="M18" t="n">
-        <v>16.94613919266722</v>
+        <v>16.91247817325604</v>
       </c>
       <c r="N18" t="n">
-        <v>541.4897776302231</v>
+        <v>540.0728091286607</v>
       </c>
       <c r="O18" t="n">
-        <v>23.269932909878</v>
+        <v>23.23946662745642</v>
       </c>
       <c r="P18" t="n">
-        <v>356.974668689276</v>
+        <v>356.8763394025769</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38551,7 +38697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S501"/>
+  <dimension ref="A1:S503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87059,6 +87205,200 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-41.03150276850768,172.1110554902128</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-41.03082267894154,172.11103419078475</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-41.03014527710866,172.11098109056323</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-41.02946809882055,172.11092527041149</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-41.02879026257954,172.11087713286688</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-41.02811481355535,172.1108007423119</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-41.02744632944807,172.11064207887168</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-41.02677418023098,172.11052668005755</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-41.02610528316868,172.1103741836424</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-41.025435880757016,172.1102284803387</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-41.0247580118356,172.1101788361177</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>-41.02408526765952,172.1100702281911</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>-41.023414161992804,172.10994271463872</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>-41.02274923107318,172.109824282742</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>-41.02209186198885,172.10964234284444</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>-41.02141228880583,172.109513089408</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>-41.02074254991581,172.1093413701441</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-41.031503379545036,172.11104827912484</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-41.03081928315961,172.11107426510338</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-41.03014318354711,172.1110057968963</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-41.02946603531217,172.11094962185882</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-41.02879016240937,172.11087831496388</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-41.02811465328355,172.11080263364784</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-41.02744559821623,172.1106507080055</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-41.026773357432155,172.11053637274915</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-41.02610522216297,172.1103748927372</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-41.02543563394644,172.11023131626848</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-41.024758669996615,172.11017127371574</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>-41.02408613149045,172.11006030263886</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>-41.0234152931907,172.1099297170225</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>-41.022751601278706,172.10980877685563</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>-41.02209512431167,172.1096281136285</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>-41.02141749005505,172.1094911865379</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>-41.02074796674731,172.10931855960885</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S503"/>
+  <dimension ref="A1:S506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32103,6 +32103,195 @@
         <v>333.6</v>
       </c>
       <c r="S503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="C504" t="n">
+        <v>359.76</v>
+      </c>
+      <c r="D504" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="E504" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="F504" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="G504" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="H504" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="I504" t="n">
+        <v>354.25</v>
+      </c>
+      <c r="J504" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="K504" t="n">
+        <v>362.69</v>
+      </c>
+      <c r="L504" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="M504" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="N504" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="O504" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="P504" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="R504" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="C505" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="D505" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="E505" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="F505" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="G505" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="H505" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="I505" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="J505" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="L505" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="M505" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="N505" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="O505" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="P505" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="R505" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="C506" t="n">
+        <v>358.12</v>
+      </c>
+      <c r="D506" t="n">
+        <v>357.02</v>
+      </c>
+      <c r="E506" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="F506" t="n">
+        <v>351.91</v>
+      </c>
+      <c r="G506" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="H506" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="I506" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="J506" t="n">
+        <v>363.58</v>
+      </c>
+      <c r="K506" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="L506" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="M506" t="n">
+        <v>366.17</v>
+      </c>
+      <c r="N506" t="n">
+        <v>369.72</v>
+      </c>
+      <c r="O506" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="P506" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>352.56</v>
+      </c>
+      <c r="R506" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="S506" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32119,7 +32308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37222,6 +37411,36 @@
       </c>
       <c r="B510" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -37390,28 +37609,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5809824459715922</v>
+        <v>-0.5764657920591071</v>
       </c>
       <c r="J2" t="n">
+        <v>505</v>
+      </c>
+      <c r="K2" t="n">
         <v>502</v>
       </c>
-      <c r="K2" t="n">
-        <v>499</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.136691123102944</v>
+        <v>0.1360619288740135</v>
       </c>
       <c r="M2" t="n">
-        <v>8.601722037796609</v>
+        <v>8.574536496086983</v>
       </c>
       <c r="N2" t="n">
-        <v>129.7652338273957</v>
+        <v>129.1140075682406</v>
       </c>
       <c r="O2" t="n">
-        <v>11.39145442107353</v>
+        <v>11.36283448652846</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6333661360567</v>
+        <v>388.5870739976669</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37468,28 +37687,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4923387462446366</v>
+        <v>-0.494951517760416</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1030544107993828</v>
+        <v>0.1050675460255667</v>
       </c>
       <c r="M3" t="n">
-        <v>9.314019412760807</v>
+        <v>9.274064632902892</v>
       </c>
       <c r="N3" t="n">
-        <v>125.9702996078192</v>
+        <v>125.2522515850315</v>
       </c>
       <c r="O3" t="n">
-        <v>11.22364912173484</v>
+        <v>11.19161523574821</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2556858400893</v>
+        <v>374.2828584581553</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37546,28 +37765,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2993366962312684</v>
+        <v>-0.3041699212249679</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04161819460409644</v>
+        <v>0.04333768599060028</v>
       </c>
       <c r="M4" t="n">
-        <v>8.464602411443531</v>
+        <v>8.440721626500078</v>
       </c>
       <c r="N4" t="n">
-        <v>125.6317441906521</v>
+        <v>125.0118448779173</v>
       </c>
       <c r="O4" t="n">
-        <v>11.2085567398596</v>
+        <v>11.18086959399479</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5311338497583</v>
+        <v>369.5805200830005</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37624,28 +37843,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09449521703640701</v>
+        <v>-0.1028367205813958</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005001758329604922</v>
+        <v>0.005964106945729131</v>
       </c>
       <c r="M5" t="n">
-        <v>8.319411848754561</v>
+        <v>8.316230948841833</v>
       </c>
       <c r="N5" t="n">
-        <v>108.15420429864</v>
+        <v>107.8893974541478</v>
       </c>
       <c r="O5" t="n">
-        <v>10.39972135677875</v>
+        <v>10.38698211484682</v>
       </c>
       <c r="P5" t="n">
-        <v>363.9754629763003</v>
+        <v>364.0607040855282</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37702,28 +37921,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09309863461175125</v>
+        <v>-0.1026537278611185</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008322415070043832</v>
+        <v>0.01013408966390794</v>
       </c>
       <c r="M6" t="n">
-        <v>6.591253357931664</v>
+        <v>6.602415172321026</v>
       </c>
       <c r="N6" t="n">
-        <v>62.88280296880134</v>
+        <v>63.00380264649117</v>
       </c>
       <c r="O6" t="n">
-        <v>7.929867777510627</v>
+        <v>7.937493473792037</v>
       </c>
       <c r="P6" t="n">
-        <v>363.2069816348718</v>
+        <v>363.3046222502301</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37780,28 +37999,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08785460346308187</v>
+        <v>-0.09530310884835884</v>
       </c>
       <c r="J7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008973726870686538</v>
+        <v>0.01059954079208103</v>
       </c>
       <c r="M7" t="n">
-        <v>6.04734464444762</v>
+        <v>6.051108772124716</v>
       </c>
       <c r="N7" t="n">
-        <v>52.05957553027004</v>
+        <v>52.05237199128752</v>
       </c>
       <c r="O7" t="n">
-        <v>7.215232188243843</v>
+        <v>7.214732981288186</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5199250838148</v>
+        <v>361.5959528305586</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37858,28 +38077,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1757884443574569</v>
+        <v>-0.1783451610886426</v>
       </c>
       <c r="J8" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K8" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04019218411286285</v>
+        <v>0.04172502889449192</v>
       </c>
       <c r="M8" t="n">
-        <v>5.38210371381911</v>
+        <v>5.365558736202206</v>
       </c>
       <c r="N8" t="n">
-        <v>45.00539882583298</v>
+        <v>44.78675844283512</v>
       </c>
       <c r="O8" t="n">
-        <v>6.708606325149284</v>
+        <v>6.692290971172363</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1202329892569</v>
+        <v>363.1463133069975</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37936,28 +38155,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1080182153031656</v>
+        <v>-0.1100421714277749</v>
       </c>
       <c r="J9" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K9" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02036253785285558</v>
+        <v>0.02132528675745815</v>
       </c>
       <c r="M9" t="n">
-        <v>4.747461785092075</v>
+        <v>4.73132384663108</v>
       </c>
       <c r="N9" t="n">
-        <v>34.23487676328423</v>
+        <v>34.07181439337219</v>
       </c>
       <c r="O9" t="n">
-        <v>5.851057747389289</v>
+        <v>5.837106679971867</v>
       </c>
       <c r="P9" t="n">
-        <v>361.4124305874868</v>
+        <v>361.4330646994389</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38014,28 +38233,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1148799534512547</v>
+        <v>-0.1127240342439066</v>
       </c>
       <c r="J10" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02605606461379162</v>
+        <v>0.02535159044188517</v>
       </c>
       <c r="M10" t="n">
-        <v>4.400759597724655</v>
+        <v>4.388767395270849</v>
       </c>
       <c r="N10" t="n">
-        <v>30.1254045427888</v>
+        <v>29.99004479220597</v>
       </c>
       <c r="O10" t="n">
-        <v>5.48866145273953</v>
+        <v>5.476316717667631</v>
       </c>
       <c r="P10" t="n">
-        <v>362.639333025522</v>
+        <v>362.6172870293175</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38092,28 +38311,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1623860908400693</v>
+        <v>-0.156794660987765</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K11" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04219912952694371</v>
+        <v>0.03968977415375829</v>
       </c>
       <c r="M11" t="n">
-        <v>4.901837222542068</v>
+        <v>4.905602177963288</v>
       </c>
       <c r="N11" t="n">
-        <v>36.48973321604409</v>
+        <v>36.45761210274114</v>
       </c>
       <c r="O11" t="n">
-        <v>6.040673241952762</v>
+        <v>6.038013920383187</v>
       </c>
       <c r="P11" t="n">
-        <v>363.8635064631247</v>
+        <v>363.8063548566992</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38170,28 +38389,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2214005447031528</v>
+        <v>-0.2182753911518499</v>
       </c>
       <c r="J12" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K12" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06858177410213173</v>
+        <v>0.0673513788216944</v>
       </c>
       <c r="M12" t="n">
-        <v>4.959150883228225</v>
+        <v>4.948399694505981</v>
       </c>
       <c r="N12" t="n">
-        <v>40.53381958439284</v>
+        <v>40.38376425616679</v>
       </c>
       <c r="O12" t="n">
-        <v>6.366617593698623</v>
+        <v>6.354822126241363</v>
       </c>
       <c r="P12" t="n">
-        <v>366.0105994423651</v>
+        <v>365.9786136337064</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38248,28 +38467,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2323730271987724</v>
+        <v>-0.2298834785682609</v>
       </c>
       <c r="J13" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K13" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05572928272963062</v>
+        <v>0.05511834104534719</v>
       </c>
       <c r="M13" t="n">
-        <v>5.826152839459023</v>
+        <v>5.809677926445026</v>
       </c>
       <c r="N13" t="n">
-        <v>55.70685539653831</v>
+        <v>55.45267332823517</v>
       </c>
       <c r="O13" t="n">
-        <v>7.463702525994609</v>
+        <v>7.446655177207762</v>
       </c>
       <c r="P13" t="n">
-        <v>367.5114807117532</v>
+        <v>367.4859864369758</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38326,28 +38545,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2381618869668374</v>
+        <v>-0.2332791219352208</v>
       </c>
       <c r="J14" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K14" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05048545804743487</v>
+        <v>0.04891453681474767</v>
       </c>
       <c r="M14" t="n">
-        <v>6.46292403073757</v>
+        <v>6.454505462524295</v>
       </c>
       <c r="N14" t="n">
-        <v>64.95371393389649</v>
+        <v>64.76778256453572</v>
       </c>
       <c r="O14" t="n">
-        <v>8.05938669713127</v>
+        <v>8.047843348657809</v>
       </c>
       <c r="P14" t="n">
-        <v>368.4332385692349</v>
+        <v>368.3832737227308</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38404,28 +38623,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.793115409946036</v>
+        <v>-1.751956662664075</v>
       </c>
       <c r="J15" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K15" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1226535259516264</v>
+        <v>0.1182270464635788</v>
       </c>
       <c r="M15" t="n">
-        <v>26.91617274027333</v>
+        <v>26.89676297739921</v>
       </c>
       <c r="N15" t="n">
-        <v>1401.642159862788</v>
+        <v>1402.514836004299</v>
       </c>
       <c r="O15" t="n">
-        <v>37.43851172072399</v>
+        <v>37.4501646992947</v>
       </c>
       <c r="P15" t="n">
-        <v>375.2484544916842</v>
+        <v>374.8278103735141</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38482,28 +38701,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5911001960919841</v>
+        <v>-0.5553578532007669</v>
       </c>
       <c r="J16" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K16" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0105692089622168</v>
+        <v>0.009413277686777466</v>
       </c>
       <c r="M16" t="n">
-        <v>35.96161618444813</v>
+        <v>35.89590413758542</v>
       </c>
       <c r="N16" t="n">
-        <v>1978.323917844041</v>
+        <v>1973.377077971216</v>
       </c>
       <c r="O16" t="n">
-        <v>44.478353362552</v>
+        <v>44.42270903458293</v>
       </c>
       <c r="P16" t="n">
-        <v>342.2247641689645</v>
+        <v>341.8567925856296</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38560,28 +38779,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.69051835393095</v>
+        <v>-1.65812826883692</v>
       </c>
       <c r="J17" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K17" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2079331566083747</v>
+        <v>0.202061062302119</v>
       </c>
       <c r="M17" t="n">
-        <v>18.3650231289943</v>
+        <v>18.3745061330932</v>
       </c>
       <c r="N17" t="n">
-        <v>658.6685930419802</v>
+        <v>660.4202569269137</v>
       </c>
       <c r="O17" t="n">
-        <v>25.66453960315634</v>
+        <v>25.69864309505297</v>
       </c>
       <c r="P17" t="n">
-        <v>364.0662002939503</v>
+        <v>363.7335193350373</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38638,28 +38857,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.424694218137992</v>
+        <v>-1.40195944282956</v>
       </c>
       <c r="J18" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K18" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1852660745733129</v>
+        <v>0.1813523133626803</v>
       </c>
       <c r="M18" t="n">
-        <v>16.91247817325604</v>
+        <v>16.8914156098287</v>
       </c>
       <c r="N18" t="n">
-        <v>540.0728091286607</v>
+        <v>539.6869936762125</v>
       </c>
       <c r="O18" t="n">
-        <v>23.23946662745642</v>
+        <v>23.23116427724216</v>
       </c>
       <c r="P18" t="n">
-        <v>356.8763394025769</v>
+        <v>356.6428063758316</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38697,7 +38916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S503"/>
+  <dimension ref="A1:S506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87399,6 +87618,297 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-41.031504711805226,172.11103255658838</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-41.0308160576547,172.11111232979184</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-41.03014011832299,172.11104196980236</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-41.02946420219118,172.110971254454</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-41.0287892308262,172.1108893084658</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-41.02811610574547,172.11078549341576</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-41.02744570840188,172.11064940772508</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-41.02677295606659,172.1105411008913</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-41.02610517132488,172.11037548364953</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-41.02543607614866,172.1102262352276</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-41.024760150857055,172.11015425831079</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-41.024087797447656,172.1100411605017</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>-41.02341707225352,172.10990927531617</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>-41.022755397167394,172.10978394411802</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>-41.022100865995526,172.10960307020508</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>-41.02142646422131,172.10945339556747</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>-41.02075505443534,172.10928871298256</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-41.03150708582746,172.1110045397362</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-41.030814434880355,172.11113148034806</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-41.030140328681874,172.1110394873481</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-41.02946316041567,172.1109835483874</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-41.028788499582745,172.11089793777353</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-41.02811633613575,172.11078277462028</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-41.02744775184239,172.1106252934328</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-41.02677572548507,172.1105084767093</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-41.026108058923846,172.11034191982776</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-41.025438955599434,172.11019314937835</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-41.024765117891405,172.11009718580146</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-41.02409298040524,172.10998160718032</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-41.023424044499315,172.109829162723</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>-41.02276393344198,172.10972809959475</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>-41.02211401965055,172.10954569798267</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>-41.021441609782805,172.1093896161892</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>-41.02077178997198,172.1092182386043</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-41.03150835798001,172.1109895264855</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-41.03081441484609,172.11113171677465</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-41.03014039880149,172.1110386598634</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-41.02946428232769,172.1109703087668</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-41.02878943116676,172.11088694427184</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-41.028117337831866,172.1107709537701</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-41.02744940462144,172.1106057892248</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-41.02677720049767,172.11049110078523</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-41.02610956372506,172.110324428821</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-41.02544005595846,172.11018050585665</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-41.02476608455732,172.11008607852128</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-41.024094193871015,172.10996766413948</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>-41.02342510369992,172.1098169922244</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>-41.022766267992516,172.109712826873</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>-41.02211631631752,172.10953568060822</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>-41.02144430471885,172.10937826754238</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>-41.02077418845917,172.10920813840875</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S506"/>
+  <dimension ref="A1:S509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32292,6 +32292,195 @@
         <v>343.33</v>
       </c>
       <c r="S506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>377.64</v>
+      </c>
+      <c r="C507" t="n">
+        <v>353.63</v>
+      </c>
+      <c r="D507" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="E507" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="F507" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="G507" t="n">
+        <v>353.45</v>
+      </c>
+      <c r="H507" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="I507" t="n">
+        <v>358.11</v>
+      </c>
+      <c r="J507" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="K507" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="L507" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="M507" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="N507" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="O507" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="P507" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>354.03</v>
+      </c>
+      <c r="R507" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="C508" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="D508" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="E508" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="F508" t="n">
+        <v>352.96</v>
+      </c>
+      <c r="G508" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="H508" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="I508" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="J508" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="K508" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="L508" t="n">
+        <v>365.77</v>
+      </c>
+      <c r="M508" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="N508" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="O508" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="P508" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="R508" t="n">
+        <v>345</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="C509" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="D509" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="E509" t="n">
+        <v>355.89</v>
+      </c>
+      <c r="F509" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="G509" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="H509" t="n">
+        <v>359.83</v>
+      </c>
+      <c r="I509" t="n">
+        <v>358.25</v>
+      </c>
+      <c r="J509" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="K509" t="n">
+        <v>367.03</v>
+      </c>
+      <c r="L509" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="M509" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="N509" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="O509" t="n">
+        <v>371.22</v>
+      </c>
+      <c r="P509" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>356.73</v>
+      </c>
+      <c r="R509" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="S509" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32308,7 +32497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37441,6 +37630,36 @@
       </c>
       <c r="B513" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>-0.93</v>
       </c>
     </row>
   </sheetData>
@@ -37609,28 +37828,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5764657920591071</v>
+        <v>-0.5733900760961862</v>
       </c>
       <c r="J2" t="n">
+        <v>508</v>
+      </c>
+      <c r="K2" t="n">
         <v>505</v>
       </c>
-      <c r="K2" t="n">
-        <v>502</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1360619288740135</v>
+        <v>0.1360596882647586</v>
       </c>
       <c r="M2" t="n">
-        <v>8.574536496086983</v>
+        <v>8.540320783750502</v>
       </c>
       <c r="N2" t="n">
-        <v>129.1140075682406</v>
+        <v>128.409465246734</v>
       </c>
       <c r="O2" t="n">
-        <v>11.36283448652846</v>
+        <v>11.33179002835536</v>
       </c>
       <c r="P2" t="n">
-        <v>388.5870739976669</v>
+        <v>388.5554359196179</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37687,28 +37906,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.494951517760416</v>
+        <v>-0.5051951088911238</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1050675460255667</v>
+        <v>0.1096251570994856</v>
       </c>
       <c r="M3" t="n">
-        <v>9.274064632902892</v>
+        <v>9.280720927093425</v>
       </c>
       <c r="N3" t="n">
-        <v>125.2522515850315</v>
+        <v>125.0851055929946</v>
       </c>
       <c r="O3" t="n">
-        <v>11.19161523574821</v>
+        <v>11.18414527771321</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2828584581553</v>
+        <v>374.3898734385107</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37765,28 +37984,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3041699212249679</v>
+        <v>-0.3127045397804198</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04333768599060028</v>
+        <v>0.0460373205848309</v>
       </c>
       <c r="M4" t="n">
-        <v>8.440721626500078</v>
+        <v>8.437755182619837</v>
       </c>
       <c r="N4" t="n">
-        <v>125.0118448779173</v>
+        <v>124.68230280648</v>
       </c>
       <c r="O4" t="n">
-        <v>11.18086959399479</v>
+        <v>11.16612299800069</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5805200830005</v>
+        <v>369.6681763223819</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37843,28 +38062,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1028367205813958</v>
+        <v>-0.1096787480326537</v>
       </c>
       <c r="J5" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005964106945729131</v>
+        <v>0.006837860214190083</v>
       </c>
       <c r="M5" t="n">
-        <v>8.316230948841833</v>
+        <v>8.304475803542374</v>
       </c>
       <c r="N5" t="n">
-        <v>107.8893974541478</v>
+        <v>107.5127580076265</v>
       </c>
       <c r="O5" t="n">
-        <v>10.38698211484682</v>
+        <v>10.36883590417104</v>
       </c>
       <c r="P5" t="n">
-        <v>364.0607040855282</v>
+        <v>364.1309500422633</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37921,28 +38140,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1026537278611185</v>
+        <v>-0.1097474463426051</v>
       </c>
       <c r="J6" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01013408966390794</v>
+        <v>0.01164325124761056</v>
       </c>
       <c r="M6" t="n">
-        <v>6.602415172321026</v>
+        <v>6.600215392900045</v>
       </c>
       <c r="N6" t="n">
-        <v>63.00380264649117</v>
+        <v>62.91343635516087</v>
       </c>
       <c r="O6" t="n">
-        <v>7.937493473792037</v>
+        <v>7.931799061698479</v>
       </c>
       <c r="P6" t="n">
-        <v>363.3046222502301</v>
+        <v>363.3774513367825</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37999,28 +38218,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09530310884835884</v>
+        <v>-0.09997421480702258</v>
       </c>
       <c r="J7" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01059954079208103</v>
+        <v>0.01175180575238133</v>
       </c>
       <c r="M7" t="n">
-        <v>6.051108772124716</v>
+        <v>6.039965134356221</v>
       </c>
       <c r="N7" t="n">
-        <v>52.05237199128752</v>
+        <v>51.87389646652158</v>
       </c>
       <c r="O7" t="n">
-        <v>7.214732981288186</v>
+        <v>7.202353536624093</v>
       </c>
       <c r="P7" t="n">
-        <v>361.5959528305586</v>
+        <v>361.6438549158011</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38077,28 +38296,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1783451610886426</v>
+        <v>-0.1781263493086815</v>
       </c>
       <c r="J8" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K8" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04172502889449192</v>
+        <v>0.04207090684048231</v>
       </c>
       <c r="M8" t="n">
-        <v>5.365558736202206</v>
+        <v>5.338240218845517</v>
       </c>
       <c r="N8" t="n">
-        <v>44.78675844283512</v>
+        <v>44.52679214589239</v>
       </c>
       <c r="O8" t="n">
-        <v>6.692290971172363</v>
+        <v>6.672839886127374</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1463133069975</v>
+        <v>363.144060043398</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38155,28 +38374,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1100421714277749</v>
+        <v>-0.1108490719710196</v>
       </c>
       <c r="J9" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K9" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02132528675745815</v>
+        <v>0.02186646961533412</v>
       </c>
       <c r="M9" t="n">
-        <v>4.73132384663108</v>
+        <v>4.70807673190826</v>
       </c>
       <c r="N9" t="n">
-        <v>34.07181439337219</v>
+        <v>33.87639458811386</v>
       </c>
       <c r="O9" t="n">
-        <v>5.837106679971867</v>
+        <v>5.820343167555833</v>
       </c>
       <c r="P9" t="n">
-        <v>361.4330646994389</v>
+        <v>361.4413467586279</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38233,28 +38452,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1127240342439066</v>
+        <v>-0.1089722826884738</v>
       </c>
       <c r="J10" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02535159044188517</v>
+        <v>0.02393024116157394</v>
       </c>
       <c r="M10" t="n">
-        <v>4.388767395270849</v>
+        <v>4.385330527696041</v>
       </c>
       <c r="N10" t="n">
-        <v>29.99004479220597</v>
+        <v>29.89078120791208</v>
       </c>
       <c r="O10" t="n">
-        <v>5.476316717667631</v>
+        <v>5.46724621797044</v>
       </c>
       <c r="P10" t="n">
-        <v>362.6172870293175</v>
+        <v>362.5787957424366</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38311,28 +38530,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.156794660987765</v>
+        <v>-0.1497856094616559</v>
       </c>
       <c r="J11" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K11" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03968977415375829</v>
+        <v>0.03647838588328034</v>
       </c>
       <c r="M11" t="n">
-        <v>4.905602177963288</v>
+        <v>4.918167153643616</v>
       </c>
       <c r="N11" t="n">
-        <v>36.45761210274114</v>
+        <v>36.51221716169312</v>
       </c>
       <c r="O11" t="n">
-        <v>6.038013920383187</v>
+        <v>6.042534001699379</v>
       </c>
       <c r="P11" t="n">
-        <v>363.8063548566992</v>
+        <v>363.7344017857336</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38389,28 +38608,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2182753911518499</v>
+        <v>-0.2118717415993685</v>
       </c>
       <c r="J12" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K12" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0673513788216944</v>
+        <v>0.06403647747104158</v>
       </c>
       <c r="M12" t="n">
-        <v>4.948399694505981</v>
+        <v>4.95304618553341</v>
       </c>
       <c r="N12" t="n">
-        <v>40.38376425616679</v>
+        <v>40.37315220290253</v>
       </c>
       <c r="O12" t="n">
-        <v>6.354822126241363</v>
+        <v>6.353987110696915</v>
       </c>
       <c r="P12" t="n">
-        <v>365.9786136337064</v>
+        <v>365.912849869493</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38467,28 +38686,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2298834785682609</v>
+        <v>-0.2237655579889858</v>
       </c>
       <c r="J13" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K13" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05511834104534719</v>
+        <v>0.05274515320942086</v>
       </c>
       <c r="M13" t="n">
-        <v>5.809677926445026</v>
+        <v>5.806512118881998</v>
       </c>
       <c r="N13" t="n">
-        <v>55.45267332823517</v>
+        <v>55.33320883986011</v>
       </c>
       <c r="O13" t="n">
-        <v>7.446655177207762</v>
+        <v>7.438629500106865</v>
       </c>
       <c r="P13" t="n">
-        <v>367.4859864369758</v>
+        <v>367.4231565918427</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38545,28 +38764,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2332791219352208</v>
+        <v>-0.223630901615673</v>
       </c>
       <c r="J14" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K14" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04891453681474767</v>
+        <v>0.04527140748336278</v>
       </c>
       <c r="M14" t="n">
-        <v>6.454505462524295</v>
+        <v>6.474809614772306</v>
       </c>
       <c r="N14" t="n">
-        <v>64.76778256453572</v>
+        <v>64.89849993991557</v>
       </c>
       <c r="O14" t="n">
-        <v>8.047843348657809</v>
+        <v>8.055960522489888</v>
       </c>
       <c r="P14" t="n">
-        <v>368.3832737227308</v>
+        <v>368.2841916069376</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38623,28 +38842,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.751956662664075</v>
+        <v>-1.708243017449977</v>
       </c>
       <c r="J15" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K15" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1182270464635788</v>
+        <v>0.1134312852711096</v>
       </c>
       <c r="M15" t="n">
-        <v>26.89676297739921</v>
+        <v>26.88532792598102</v>
       </c>
       <c r="N15" t="n">
-        <v>1402.514836004299</v>
+        <v>1404.68486802942</v>
       </c>
       <c r="O15" t="n">
-        <v>37.4501646992947</v>
+        <v>37.47912576394252</v>
       </c>
       <c r="P15" t="n">
-        <v>374.8278103735141</v>
+        <v>374.3789301287746</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38701,28 +38920,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5553578532007669</v>
+        <v>-0.5174975704655556</v>
       </c>
       <c r="J16" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K16" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L16" t="n">
-        <v>0.009413277686777466</v>
+        <v>0.008242636619041122</v>
       </c>
       <c r="M16" t="n">
-        <v>35.89590413758542</v>
+        <v>35.83956383125184</v>
       </c>
       <c r="N16" t="n">
-        <v>1973.377077971216</v>
+        <v>1969.414649282258</v>
       </c>
       <c r="O16" t="n">
-        <v>44.42270903458293</v>
+        <v>44.37808749013704</v>
       </c>
       <c r="P16" t="n">
-        <v>341.8567925856296</v>
+        <v>341.4651753398402</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38779,28 +38998,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.65812826883692</v>
+        <v>-1.621251398968392</v>
       </c>
       <c r="J17" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K17" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L17" t="n">
-        <v>0.202061062302119</v>
+        <v>0.1949128355107504</v>
       </c>
       <c r="M17" t="n">
-        <v>18.3745061330932</v>
+        <v>18.40227774343988</v>
       </c>
       <c r="N17" t="n">
-        <v>660.4202569269137</v>
+        <v>663.8901075769104</v>
       </c>
       <c r="O17" t="n">
-        <v>25.69864309505297</v>
+        <v>25.7660650386688</v>
       </c>
       <c r="P17" t="n">
-        <v>363.7335193350373</v>
+        <v>363.3529740472541</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38857,28 +39076,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.40195944282956</v>
+        <v>-1.37452933604016</v>
       </c>
       <c r="J18" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K18" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1813523133626803</v>
+        <v>0.1760866296616115</v>
       </c>
       <c r="M18" t="n">
-        <v>16.8914156098287</v>
+        <v>16.88608631828288</v>
       </c>
       <c r="N18" t="n">
-        <v>539.6869936762125</v>
+        <v>540.5753055919123</v>
       </c>
       <c r="O18" t="n">
-        <v>23.23116427724216</v>
+        <v>23.25027538744245</v>
       </c>
       <c r="P18" t="n">
-        <v>356.6428063758316</v>
+        <v>356.3597463373134</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38916,7 +39135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S506"/>
+  <dimension ref="A1:S509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87909,6 +88128,297 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-41.03150687547134,172.11100702224218</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-41.030809917139976,172.1111847945462</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-41.03013847551845,172.1110613565873</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-41.02946440253246,172.110968890236</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-41.02879043286881,172.11087512330198</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-41.02811803901842,172.11076267917477</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-41.027449855378805,172.11060046989516</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-41.02677682923624,172.1104954743172</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-41.026109248530425,172.11032809247786</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-41.02543976801418,172.1101838144418</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-41.02476655760621,172.11008064304363</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-41.024094738901695,172.10996140158713</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>-41.0234261834662,172.10980458540507</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>-41.02276824612152,172.10969988586368</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>-41.02211845639278,172.10952634623592</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>-41.021448266272756,172.10936158502992</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>-41.02077871593817,172.10918907286907</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-41.03150568345229,172.11102108977568</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-41.0308077233724,172.1112106832564</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-41.0301355505169,172.11109587451924</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-41.02946462290782,172.11096628959618</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-41.02879048295388,172.1108745322535</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-41.028118319492876,172.1107593693366</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-41.02744939460461,172.1106059074321</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-41.02677548466644,172.1105113135948</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-41.026108638475975,172.1103351834266</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-41.02543941836743,172.11018783200944</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-41.02476651647153,172.11008111569387</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-41.02409480060326,172.1099606926189</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>-41.023426430269716,172.1098017495606</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>-41.02276591157271,172.1097151585863</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>-41.022116368514496,172.1095354529406</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>-41.02144877831017,172.10935942878666</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>-41.020778688988905,172.10918918635446</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-41.031503609936046,172.11104556019</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-41.03080510887466,172.11124153692253</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-41.030135600602634,172.1110952834588</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-41.029466345840454,172.1109459573207</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-41.028792676677014,172.11084864432826</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-41.028120943927796,172.11072839870664</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-41.02745148812002,172.11058120210066</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-41.02677696971355,172.11049381946725</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-41.02610977724394,172.11032194698888</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-41.02544053929329,172.11017495216007</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-41.02476828526083,172.11006079173333</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-41.02409644597673,172.1099417867998</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>-41.02342820930975,172.10978130784778</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>-41.02276926191691,172.10969324048023</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>-41.02211882177141,172.10952475256255</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>-41.02145554258995,172.10933094367533</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>-41.02078378239899,172.1091677376193</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0335/nzd0335.xlsx
+++ b/data/nzd0335/nzd0335.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S509"/>
+  <dimension ref="A1:S514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32481,6 +32481,321 @@
         <v>346.89</v>
       </c>
       <c r="S509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="C510" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="D510" t="n">
+        <v>352.57</v>
+      </c>
+      <c r="E510" t="n">
+        <v>356.38</v>
+      </c>
+      <c r="F510" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="G510" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="H510" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="I510" t="n">
+        <v>359.08</v>
+      </c>
+      <c r="J510" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="K510" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="L510" t="n">
+        <v>367.94</v>
+      </c>
+      <c r="M510" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="N510" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="O510" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="P510" t="n">
+        <v>362.68</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="R510" t="n">
+        <v>347</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="C511" t="n">
+        <v>345.31</v>
+      </c>
+      <c r="D511" t="n">
+        <v>352.12</v>
+      </c>
+      <c r="E511" t="n">
+        <v>357.02</v>
+      </c>
+      <c r="F511" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="G511" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="H511" t="n">
+        <v>359.42</v>
+      </c>
+      <c r="I511" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="J511" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="K511" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="L511" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="M511" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="N511" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="O511" t="n">
+        <v>354.02</v>
+      </c>
+      <c r="P511" t="n">
+        <v>349.11</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>346.99</v>
+      </c>
+      <c r="R511" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="C512" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="D512" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="E512" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="F512" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="G512" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="H512" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="I512" t="n">
+        <v>358.97</v>
+      </c>
+      <c r="J512" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="K512" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="L512" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="M512" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="N512" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="O512" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="P512" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="R512" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="C513" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="D513" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="E513" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="F513" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="G513" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="H513" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="I513" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="J513" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="K513" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="L513" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="M513" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="N513" t="n">
+        <v>354.25</v>
+      </c>
+      <c r="O513" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="P513" t="n">
+        <v>328.63</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="R513" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="C514" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="D514" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="E514" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="F514" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="G514" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="H514" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="I514" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="J514" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="K514" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="L514" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="M514" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="N514" t="n">
+        <v>354.25</v>
+      </c>
+      <c r="O514" t="n">
+        <v>315.98</v>
+      </c>
+      <c r="P514" t="n">
+        <v>319.93</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>322.79</v>
+      </c>
+      <c r="R514" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="S514" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32497,7 +32812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37660,6 +37975,56 @@
       </c>
       <c r="B516" t="n">
         <v>-0.93</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -37828,28 +38193,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5733900760961862</v>
+        <v>-0.5739732107471578</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1360596882647586</v>
+        <v>0.1384631214460157</v>
       </c>
       <c r="M2" t="n">
-        <v>8.540320783750502</v>
+        <v>8.464692230637919</v>
       </c>
       <c r="N2" t="n">
-        <v>128.409465246734</v>
+        <v>127.1573082606783</v>
       </c>
       <c r="O2" t="n">
-        <v>11.33179002835536</v>
+        <v>11.27640493511466</v>
       </c>
       <c r="P2" t="n">
-        <v>388.5554359196179</v>
+        <v>388.5614784581279</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37906,28 +38271,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5051951088911238</v>
+        <v>-0.5295310239102324</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1096251570994856</v>
+        <v>0.1194536332944014</v>
       </c>
       <c r="M3" t="n">
-        <v>9.280720927093425</v>
+        <v>9.33607623861862</v>
       </c>
       <c r="N3" t="n">
-        <v>125.0851055929946</v>
+        <v>125.7983310178031</v>
       </c>
       <c r="O3" t="n">
-        <v>11.18414527771321</v>
+        <v>11.21598551255319</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3898734385107</v>
+        <v>374.6450758715309</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37984,28 +38349,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3127045397804198</v>
+        <v>-0.3275347888002068</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0460373205848309</v>
+        <v>0.05087877841089783</v>
       </c>
       <c r="M4" t="n">
-        <v>8.437755182619837</v>
+        <v>8.439338369856845</v>
       </c>
       <c r="N4" t="n">
-        <v>124.68230280648</v>
+        <v>124.2039945789701</v>
       </c>
       <c r="O4" t="n">
-        <v>11.16612299800069</v>
+        <v>11.14468458858169</v>
       </c>
       <c r="P4" t="n">
-        <v>369.6681763223819</v>
+        <v>369.8210719716414</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38062,28 +38427,28 @@
         <v>0.1839</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1096787480326537</v>
+        <v>-0.1168550354724428</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006837860214190083</v>
+        <v>0.007884538912492856</v>
       </c>
       <c r="M5" t="n">
-        <v>8.304475803542374</v>
+        <v>8.262434303891171</v>
       </c>
       <c r="N5" t="n">
-        <v>107.5127580076265</v>
+        <v>106.6390985330796</v>
       </c>
       <c r="O5" t="n">
-        <v>10.36883590417104</v>
+        <v>10.32662086711232</v>
       </c>
       <c r="P5" t="n">
-        <v>364.1309500422633</v>
+        <v>364.2049330939578</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38140,28 +38505,28 @@
         <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1097474463426051</v>
+        <v>-0.1164211422758004</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01164325124761056</v>
+        <v>0.01329069988701681</v>
       </c>
       <c r="M6" t="n">
-        <v>6.600215392900045</v>
+        <v>6.570021654953155</v>
       </c>
       <c r="N6" t="n">
-        <v>62.91343635516087</v>
+        <v>62.45119708362066</v>
       </c>
       <c r="O6" t="n">
-        <v>7.931799061698479</v>
+        <v>7.90260698020727</v>
       </c>
       <c r="P6" t="n">
-        <v>363.3774513367825</v>
+        <v>363.4462500518508</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38218,28 +38583,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09997421480702258</v>
+        <v>-0.1026682268355335</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K7" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01175180575238133</v>
+        <v>0.01260546346360114</v>
       </c>
       <c r="M7" t="n">
-        <v>6.039965134356221</v>
+        <v>5.994903888295076</v>
       </c>
       <c r="N7" t="n">
-        <v>51.87389646652158</v>
+        <v>51.39303734104691</v>
       </c>
       <c r="O7" t="n">
-        <v>7.202353536624093</v>
+        <v>7.168893732023576</v>
       </c>
       <c r="P7" t="n">
-        <v>361.6438549158011</v>
+        <v>361.6715921444534</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38296,28 +38661,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1781263493086815</v>
+        <v>-0.1757500271387226</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K8" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04207090684048231</v>
+        <v>0.04171105146629972</v>
       </c>
       <c r="M8" t="n">
-        <v>5.338240218845517</v>
+        <v>5.298853333047568</v>
       </c>
       <c r="N8" t="n">
-        <v>44.52679214589239</v>
+        <v>44.1118214905914</v>
       </c>
       <c r="O8" t="n">
-        <v>6.672839886127374</v>
+        <v>6.641673094227944</v>
       </c>
       <c r="P8" t="n">
-        <v>363.144060043398</v>
+        <v>363.119577928808</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38374,28 +38739,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1108490719710196</v>
+        <v>-0.1101324860787946</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K9" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02186646961533412</v>
+        <v>0.02197999492202629</v>
       </c>
       <c r="M9" t="n">
-        <v>4.70807673190826</v>
+        <v>4.666063585250813</v>
       </c>
       <c r="N9" t="n">
-        <v>33.87639458811386</v>
+        <v>33.54825104196009</v>
       </c>
       <c r="O9" t="n">
-        <v>5.820343167555833</v>
+        <v>5.792085206724785</v>
       </c>
       <c r="P9" t="n">
-        <v>361.4413467586279</v>
+        <v>361.4339647630046</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38452,28 +38817,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1089722826884738</v>
+        <v>-0.1030369974886741</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02393024116157394</v>
+        <v>0.02175018175708365</v>
       </c>
       <c r="M10" t="n">
-        <v>4.385330527696041</v>
+        <v>4.377558407967529</v>
       </c>
       <c r="N10" t="n">
-        <v>29.89078120791208</v>
+        <v>29.71894917297568</v>
       </c>
       <c r="O10" t="n">
-        <v>5.46724621797044</v>
+        <v>5.451508889562199</v>
       </c>
       <c r="P10" t="n">
-        <v>362.5787957424366</v>
+        <v>362.517667935901</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38530,28 +38895,28 @@
         <v>0.1996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1497856094616559</v>
+        <v>-0.1390732144310085</v>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K11" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03647838588328034</v>
+        <v>0.03183952035651383</v>
       </c>
       <c r="M11" t="n">
-        <v>4.918167153643616</v>
+        <v>4.934005751463765</v>
       </c>
       <c r="N11" t="n">
-        <v>36.51221716169312</v>
+        <v>36.54636350450201</v>
       </c>
       <c r="O11" t="n">
-        <v>6.042534001699379</v>
+        <v>6.045358840011237</v>
       </c>
       <c r="P11" t="n">
-        <v>363.7344017857336</v>
+        <v>363.6240088777765</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38608,28 +38973,28 @@
         <v>0.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2118717415993685</v>
+        <v>-0.1995813169408206</v>
       </c>
       <c r="J12" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K12" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06403647747104158</v>
+        <v>0.05754030919969111</v>
       </c>
       <c r="M12" t="n">
-        <v>4.95304618553341</v>
+        <v>4.97103727737298</v>
       </c>
       <c r="N12" t="n">
-        <v>40.37315220290253</v>
+        <v>40.49170333083016</v>
       </c>
       <c r="O12" t="n">
-        <v>6.353987110696915</v>
+        <v>6.363309149399403</v>
       </c>
       <c r="P12" t="n">
-        <v>365.912849869493</v>
+        <v>365.7861528508294</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38686,28 +39051,28 @@
         <v>0.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2237655579889858</v>
+        <v>-0.2128726104048039</v>
       </c>
       <c r="J13" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K13" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05274515320942086</v>
+        <v>0.04848453354942273</v>
       </c>
       <c r="M13" t="n">
-        <v>5.806512118881998</v>
+        <v>5.804828618618088</v>
       </c>
       <c r="N13" t="n">
-        <v>55.33320883986011</v>
+        <v>55.19349389989289</v>
       </c>
       <c r="O13" t="n">
-        <v>7.438629500106865</v>
+        <v>7.429232389681514</v>
       </c>
       <c r="P13" t="n">
-        <v>367.4231565918427</v>
+        <v>367.3108640914908</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38764,28 +39129,28 @@
         <v>0.1929</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.223630901615673</v>
+        <v>-0.2197635557918575</v>
       </c>
       <c r="J14" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K14" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04527140748336278</v>
+        <v>0.04406874224920954</v>
       </c>
       <c r="M14" t="n">
-        <v>6.474809614772306</v>
+        <v>6.498324974479376</v>
       </c>
       <c r="N14" t="n">
-        <v>64.89849993991557</v>
+        <v>65.01941220228994</v>
       </c>
       <c r="O14" t="n">
-        <v>8.055960522489888</v>
+        <v>8.06346155210589</v>
       </c>
       <c r="P14" t="n">
-        <v>368.2841916069376</v>
+        <v>368.2445068011108</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38842,28 +39207,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.708243017449977</v>
+        <v>-1.68675360029696</v>
       </c>
       <c r="J15" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K15" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1134312852711096</v>
+        <v>0.1123606687098421</v>
       </c>
       <c r="M15" t="n">
-        <v>26.88532792598102</v>
+        <v>26.75167513126457</v>
       </c>
       <c r="N15" t="n">
-        <v>1404.68486802942</v>
+        <v>1396.141560577269</v>
       </c>
       <c r="O15" t="n">
-        <v>37.47912576394252</v>
+        <v>37.36497772750934</v>
       </c>
       <c r="P15" t="n">
-        <v>374.3789301287746</v>
+        <v>374.1578564397496</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38920,28 +39285,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5174975704655556</v>
+        <v>-0.4972352039294529</v>
       </c>
       <c r="J16" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K16" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008242636619041122</v>
+        <v>0.007740443153243071</v>
       </c>
       <c r="M16" t="n">
-        <v>35.83956383125184</v>
+        <v>35.60271938558082</v>
       </c>
       <c r="N16" t="n">
-        <v>1969.414649282258</v>
+        <v>1953.66835487243</v>
       </c>
       <c r="O16" t="n">
-        <v>44.37808749013704</v>
+        <v>44.2003207553116</v>
       </c>
       <c r="P16" t="n">
-        <v>341.4651753398402</v>
+        <v>341.2551259181852</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38998,28 +39363,28 @@
         <v>0.1415</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.621251398968392</v>
+        <v>-1.5891750757228</v>
       </c>
       <c r="J17" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K17" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1949128355107504</v>
+        <v>0.1904157678941961</v>
       </c>
       <c r="M17" t="n">
-        <v>18.40227774343988</v>
+        <v>18.34022507377374</v>
       </c>
       <c r="N17" t="n">
-        <v>663.8901075769104</v>
+        <v>662.2571598446935</v>
       </c>
       <c r="O17" t="n">
-        <v>25.7660650386688</v>
+        <v>25.734357575908</v>
       </c>
       <c r="P17" t="n">
-        <v>363.3529740472541</v>
+        <v>363.0209576075364</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -39076,28 +39441,28 @@
         <v>0.0944</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.37452933604016</v>
+        <v>-1.355924926108828</v>
       </c>
       <c r="J18" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="K18" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1760866296616115</v>
+        <v>0.1741873728023597</v>
       </c>
       <c r="M18" t="n">
-        <v>16.88608631828288</v>
+        <v>16.79916876288667</v>
       </c>
       <c r="N18" t="n">
-        <v>540.5753055919123</v>
+        <v>537.6011374025068</v>
       </c>
       <c r="O18" t="n">
-        <v>23.25027538744245</v>
+        <v>23.18622732146191</v>
       </c>
       <c r="P18" t="n">
-        <v>356.3597463373134</v>
+        <v>356.1672721787331</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -39135,7 +39500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S509"/>
+  <dimension ref="A1:S514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88419,6 +88784,491 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-41.031503609936046,172.11104556019</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-41.03080510887466,172.11124153692253</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-41.03013594118551,172.1110912642477</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-41.02946683667526,172.11094016498623</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-41.02879342795072,172.11083977860005</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-41.02812122440125,172.11072508886818</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-41.02745181867459,172.1105773012587</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-41.02677780254286,172.1104840085711</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-41.02610991958982,172.11032029243415</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-41.025440518725866,172.1101751884876</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-41.02476874802487,172.1100554744179</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-41.024096723633185,172.10993859644273</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-41.02342816817593,172.10978178048856</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>-41.02276808573273,172.10970093513475</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>-41.02211579434784,172.10953795728426</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>-41.02145656666356,172.10932663118788</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>-41.02078407884072,172.1091664892801</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-41.03150167665293,172.1110683755992</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-41.03080158279565,172.11128314799356</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-41.03013549041402,172.1110965837918</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-41.02946747776518,172.11093259948802</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-41.0287938085958,172.11083528663102</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-41.02812162507746,172.1107203605275</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-41.02745107743082,172.1105860486012</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-41.02677720049767,172.11049110078523</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-41.02610904517899,172.11033045612746</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-41.02543970631183,172.11018452342435</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-41.02476865547209,172.11005653788098</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-41.024096312290254,172.1099433228976</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-41.02342718096337,172.1097931238669</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-41.022738609675294,172.10989376775356</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>-41.02208037859843,172.10969242967363</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>-41.021429293910764,172.10944147949365</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>-41.020759339383645,172.1092706688214</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-41.03150167665293,172.1110683755992</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-41.03080262459328,172.11127085381392</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-41.03013592115125,172.11109150067188</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-41.02946811885459,172.11092503398967</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-41.028794359529165,172.11082878509683</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-41.028122085854875,172.1107149229356</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-41.02745127776704,172.1105836844546</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-41.02677769216794,172.11048530881038</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-41.02610899434113,172.11033104703986</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-41.02543985028399,172.11018286913176</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-41.02476909766866,172.11005145689066</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-41.02409582896203,172.10994887648204</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-41.02342547390564,172.10981273845783</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-41.02271198471083,172.1100679465298</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>-41.02205031289035,172.1098235660184</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>-41.021402991225514,172.1095522421985</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>-41.020735246618386,172.10937212464108</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-41.03150167665293,172.1110683755992</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-41.03080262459328,172.11127085381392</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-41.03013592115125,172.11109150067188</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-41.02946723735651,172.11093543654988</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-41.028794589919364,172.1108260662734</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-41.02812256666581,172.11070924892667</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-41.0274517886242,172.1105776558807</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-41.02677806342898,172.11048093527828</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-41.026109360373695,172.1103267924706</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-41.02543959319082,172.11018582322563</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-41.02476839838096,172.1100594919451</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-41.02409549988736,172.1099526576459</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-41.02340919498823,172.10999978598488</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-41.02269108018567,172.1102047012569</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>-41.02202692834661,172.1099255608724</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>-41.02138423432693,172.1096312286648</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>-41.020718699633406,172.1094418045468</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-41.03150167665293,172.1110683755992</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-41.03080262459328,172.11127085381392</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-41.03013592115125,172.11109150067188</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-41.02946723735651,172.11093543654988</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-41.02879377854487,172.11083564126017</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-41.02812227617591,172.11071267697375</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-41.02745123769979,172.11058415728394</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-41.026777330940824,172.11048956413885</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-41.02610850629746,172.1103367197988</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-41.02543819460265,172.1102018934959</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-41.02476678384689,172.11007804346733</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-41.02409549988736,172.1099526576459</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-41.02340919498823,172.10999978598488</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-41.022670817075834,172.11033725882808</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>-41.022004222285055,172.11002459598666</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>-41.02136407598993,172.10971611636978</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>-41.020701128521374,172.10951579685226</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
